--- a/ConfigExporter/xlsx/duel_handicap.xlsx
+++ b/ConfigExporter/xlsx/duel_handicap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>贴目</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>星位坐标</t>
         </is>
       </c>
@@ -466,6 +471,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>komi</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>stonePoints</t>
         </is>
       </c>
@@ -493,6 +503,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>list(string)</t>
         </is>
       </c>
@@ -523,6 +538,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -543,7 +563,10 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -552,7 +575,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>9x9_2</t>
+          <t>9x9_sen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -562,22 +585,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>让2子</t>
+          <t>让先</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>[C3,G7]</t>
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9x9_3</t>
+          <t>9x9_2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -587,22 +613,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>让3子</t>
+          <t>让2子</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[C3,G7,G3]</t>
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>[C3,G7]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>9x9_4</t>
+          <t>9x9_3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -612,22 +641,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>让4子</t>
+          <t>让3子</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[C3,G3,C7,G7]</t>
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>[C3,G7,G3]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>9x9_5</t>
+          <t>9x9_4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -637,47 +669,53 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>让5子</t>
+          <t>让4子</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>[C3,G3,C7,G7,E5]</t>
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>[C3,G3,C7,G7]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13x13_0</t>
+          <t>9x9_5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13x13</t>
+          <t>9x9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>分先</t>
+          <t>让5子</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>[]</t>
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>[C3,G3,C7,G7,E5]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13x13_2</t>
+          <t>13x13_0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -687,22 +725,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>让2子</t>
+          <t>分先</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>[D4,K10]</t>
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13x13_3</t>
+          <t>13x13_sen</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -712,22 +753,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>让3子</t>
+          <t>让先</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>[D4,K10,K4]</t>
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13x13_4</t>
+          <t>13x13_2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -737,22 +781,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>让4子</t>
+          <t>让2子</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[D4,K4,D10,K10]</t>
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>[D4,K10]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13x13_5</t>
+          <t>13x13_3</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -762,22 +809,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>让5子</t>
+          <t>让3子</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>[D4,K4,D10,K10,G7]</t>
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>[D4,K10,K4]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13x13_6</t>
+          <t>13x13_4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -787,22 +837,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>让6子</t>
+          <t>让4子</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>[D4,K4,D10,K10,D7,K7]</t>
+        <v>4</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>[D4,K4,D10,K10]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13x13_7</t>
+          <t>13x13_5</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -812,22 +865,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>让7子</t>
+          <t>让5子</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>[D4,K4,D10,K10,D7,K7,G7]</t>
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>[D4,K4,D10,K10,G7]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13x13_8</t>
+          <t>13x13_6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -837,22 +893,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>让8子</t>
+          <t>让6子</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>[D4,K4,D10,K10,D7,K7,G4,G10]</t>
+        <v>6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>[D4,K4,D10,K10,D7,K7]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13x13_9</t>
+          <t>13x13_7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -862,72 +921,81 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>让9子</t>
+          <t>让7子</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>[D4,G4,K4,D7,G7,K7,D10,G10,K10]</t>
+        <v>7</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>[D4,K4,D10,K10,D7,K7,G7]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19x19_0</t>
+          <t>13x13_8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>19x19</t>
+          <t>13x13</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>分先</t>
+          <t>让8子</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>[]</t>
+        <v>8</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>[D4,K4,D10,K10,D7,K7,G4,G10]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19x19_2</t>
+          <t>13x13_9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19x19</t>
+          <t>13x13</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>让2子</t>
+          <t>让9子</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[D4,Q16]</t>
+        <v>9</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>[D4,G4,K4,D7,G7,K7,D10,G10,K10]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19x19_3</t>
+          <t>19x19_0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -937,22 +1005,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>让3子</t>
+          <t>分先</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4]</t>
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19x19_4</t>
+          <t>19x19_sen</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -962,22 +1033,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>让4子</t>
+          <t>让先</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>4</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4,D16]</t>
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>[]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19x19_5</t>
+          <t>19x19_2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -987,22 +1061,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>让5子</t>
+          <t>让2子</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4,D16,K10]</t>
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>[D4,Q16]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>19x19_6</t>
+          <t>19x19_3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1012,22 +1089,25 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>让6子</t>
+          <t>让3子</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4,D16,D10,Q10]</t>
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>19x19_7</t>
+          <t>19x19_4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1037,22 +1117,25 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>让7子</t>
+          <t>让4子</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4,D16,D10,Q10,K10]</t>
+        <v>4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4,D16]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>19x19_8</t>
+          <t>19x19_5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1062,38 +1145,128 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>让8子</t>
+          <t>让5子</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>[D4,Q16,Q4,D16,D10,Q10,K4,K16]</t>
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4,D16,K10]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>19x19_6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>19x19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>让6子</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4,D16,D10,Q10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>19x19_7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>19x19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>让7子</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4,D16,D10,Q10,K10]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>19x19_8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>19x19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>让8子</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>[D4,Q16,Q4,D16,D10,Q10,K4,K16]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>19x19_9</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>19x19</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>让9子</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D30" t="n">
         <v>9</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>[D4,D10,D16,K4,K10,K16,Q4,Q10,Q16]</t>
         </is>

--- a/ConfigExporter/xlsx/duel_handicap.xlsx
+++ b/ConfigExporter/xlsx/duel_handicap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>星位坐标</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>OGS启用</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>stonePoints</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ogsEnabled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +521,11 @@
           <t>list(string)</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +558,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>#require</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -571,6 +591,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -599,6 +624,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -627,6 +657,11 @@
           <t>[C3,G7]</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -655,6 +690,11 @@
           <t>[C3,G7,G3]</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -683,6 +723,11 @@
           <t>[C3,G3,C7,G7]</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -711,6 +756,11 @@
           <t>[C3,G3,C7,G7,E5]</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -739,6 +789,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -767,6 +822,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -795,6 +855,11 @@
           <t>[D4,K10]</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -823,6 +888,11 @@
           <t>[D4,K10,K4]</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -851,6 +921,11 @@
           <t>[D4,K4,D10,K10]</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -879,6 +954,11 @@
           <t>[D4,K4,D10,K10,G7]</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -907,6 +987,11 @@
           <t>[D4,K4,D10,K10,D7,K7]</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -935,6 +1020,11 @@
           <t>[D4,K4,D10,K10,D7,K7,G7]</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -963,6 +1053,11 @@
           <t>[D4,K4,D10,K10,D7,K7,G4,G10]</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -991,6 +1086,11 @@
           <t>[D4,G4,K4,D7,G7,K7,D10,G10,K10]</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1019,6 +1119,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1047,6 +1152,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1075,6 +1185,11 @@
           <t>[D4,Q16]</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1103,6 +1218,11 @@
           <t>[D4,Q16,Q4]</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1131,6 +1251,11 @@
           <t>[D4,Q16,Q4,D16]</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1159,6 +1284,11 @@
           <t>[D4,Q16,Q4,D16,K10]</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1187,6 +1317,11 @@
           <t>[D4,Q16,Q4,D16,D10,Q10]</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1215,6 +1350,11 @@
           <t>[D4,Q16,Q4,D16,D10,Q10,K10]</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1243,6 +1383,11 @@
           <t>[D4,Q16,Q4,D16,D10,Q10,K4,K16]</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1269,6 +1414,11 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>[D4,D10,D16,K4,K10,K16,Q4,Q10,Q16]</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>

--- a/ConfigExporter/xlsx/duel_handicap.xlsx
+++ b/ConfigExporter/xlsx/duel_handicap.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>OGS启用</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>OGS好友启用</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>ogsEnabled</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ogsFriendEnabled</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>boolean</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +578,11 @@
           <t>#require</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -596,6 +616,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -629,6 +654,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -662,6 +692,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -695,6 +730,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,6 +768,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -761,6 +806,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -794,6 +844,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -827,6 +882,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -860,6 +920,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -893,6 +958,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -926,6 +996,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -959,6 +1034,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -992,6 +1072,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1025,6 +1110,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1058,6 +1148,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1091,6 +1186,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1124,6 +1224,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1157,6 +1262,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1190,6 +1300,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1223,6 +1338,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1256,6 +1376,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1289,6 +1414,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1322,6 +1452,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1355,6 +1490,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1388,6 +1528,11 @@
           <t>True</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1417,6 +1562,11 @@
         </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>True</t>
         </is>
